--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网管服务器配置表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网管服务器配置表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,14 +450,8 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -476,6 +470,27 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网管服务器配置表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网管服务器配置表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,17 +480,32 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>自动解析</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>V2.2_20260614213043_DRB</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网管服务器配置表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网管服务器配置表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,8 +450,14 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -495,17 +501,26 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
         </is>
       </c>
     </row>
